--- a/artfynd/A 39613-2023 artfynd.xlsx
+++ b/artfynd/A 39613-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39613-2023 artfynd.xlsx
+++ b/artfynd/A 39613-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66161869</v>
+        <v>116768954</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trosta, Upl</t>
+          <t>Seminghundra häradsallmänning 1:24, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670313.1318495639</v>
+        <v>670459</v>
       </c>
       <c r="R2" t="n">
-        <v>6615684.917853329</v>
+        <v>6615613</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66161872</v>
+        <v>114398505</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trosta, Upl</t>
+          <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670057.0068101605</v>
+        <v>670454</v>
       </c>
       <c r="R3" t="n">
-        <v>6615651.996833541</v>
+        <v>6615606</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +862,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114358242</v>
+        <v>114398386</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +889,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,25 +906,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>eDNA</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trosta gård, Upl</t>
+          <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670316</v>
+        <v>670287</v>
       </c>
       <c r="R4" t="n">
-        <v>6615652</v>
+        <v>6615579</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>Kacklande par på håll</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,78 +977,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mika Thunell, Arvid de Jong</t>
+          <t>Caroline Kling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Groddjursinventering Trosta AKE0020b</t>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114398374</v>
+        <v>66161870</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trosta Gård, Upl</t>
+          <t>Trosta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670368</v>
+        <v>669912</v>
       </c>
       <c r="R5" t="n">
-        <v>6615642</v>
+        <v>6615502</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,17 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förra gången! Lägg rosa punkt här</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,31 +1078,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Hanna Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Caroline Kling</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
-        </is>
-      </c>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114398583</v>
+        <v>114398491</v>
       </c>
       <c r="B6" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,16 +1101,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,14 +1118,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670361</v>
+        <v>670304</v>
       </c>
       <c r="R6" t="n">
-        <v>6615676</v>
+        <v>6615754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1160,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,12 +1199,7 @@
         <v>114398494</v>
       </c>
       <c r="B7" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114398636</v>
+        <v>114398374</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1330,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1406,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670373</v>
+        <v>670368</v>
       </c>
       <c r="R8" t="n">
-        <v>6615708</v>
+        <v>6615642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,12 +1376,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förra gången! Lägg rosa punkt här</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114398637</v>
+        <v>114398636</v>
       </c>
       <c r="B9" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670363</v>
+        <v>670373</v>
       </c>
       <c r="R9" t="n">
-        <v>6615646</v>
+        <v>6615708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,50 +1523,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116768947</v>
+        <v>114398637</v>
       </c>
       <c r="B10" t="n">
-        <v>96730</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Seminghundra häradsallmänning 1:28, Upl</t>
+          <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670425</v>
+        <v>670363</v>
       </c>
       <c r="R10" t="n">
-        <v>6615621</v>
+        <v>6615646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,12 +1593,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,62 +1613,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116768954</v>
+        <v>114398626</v>
       </c>
       <c r="B11" t="n">
-        <v>74539</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>306</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Seminghundra häradsallmänning 1:24, Upl</t>
+          <t>Trosta Gård, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670459</v>
+        <v>670425</v>
       </c>
       <c r="R11" t="n">
-        <v>6615613</v>
+        <v>6615703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,12 +1699,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,15 +1719,638 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114398583</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trosta Gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>670361</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6615676</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114358242</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Trosta gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>670316</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6615652</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mika Thunell, Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Groddjursinventering Trosta AKE0020b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>66161869</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Trosta, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>670313</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6615685</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-04-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-04-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>66161872</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Trosta, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>670057</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6615652</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-04-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-04-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>116768947</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Seminghundra häradsallmänning 1:28, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>670425</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6615621</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Lilian Karlsson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Lilian Karlsson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6657962</v>
+      </c>
+      <c r="B17" t="n">
+        <v>89076</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>239203</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hygrocybe acutoconica var. acutoconica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Trosta gård 800 m SSV längs vägen mot Kimsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>670055</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6615820</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2008-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2008-08-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Vägren, sandig med Hieracium pilosella</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39613-2023 artfynd.xlsx
+++ b/artfynd/A 39613-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116768954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66161870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398494</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398374</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398636</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398637</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398626</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>AKE0020_Trosta_Gård_fågelinventering_2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114398583</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
           <t>Groddjursinventering Trosta AKE0020b</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358242</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66161869</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66161872</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2244,6 +2319,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116768947</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,8 +2431,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6657962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>